--- a/data/trans_dic/IP04D$notiene-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,34; 16,03</t>
+          <t>5,44; 15,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,19; 34,18</t>
+          <t>15,28; 33,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,8; 48,37</t>
+          <t>11,33; 51,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,11; 17,3</t>
+          <t>6,13; 18,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,87; 32,74</t>
+          <t>15,24; 32,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,75; 22,65</t>
+          <t>6,22; 23,33</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,14; 14,95</t>
+          <t>6,75; 14,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,79; 30,13</t>
+          <t>17,25; 29,73</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 32,01</t>
+          <t>11,14; 32,31</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,9</t>
+          <t>1,99; 4,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 16,24</t>
+          <t>11,03; 16,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 16,04</t>
+          <t>9,88; 16,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,58; 5,58</t>
+          <t>2,69; 5,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 18,1</t>
+          <t>12,55; 18,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,87; 18,22</t>
+          <t>10,88; 18,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,66; 4,65</t>
+          <t>2,74; 4,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,6; 16,31</t>
+          <t>12,61; 16,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,45; 16,21</t>
+          <t>11,3; 15,94</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 6,73</t>
+          <t>1,4; 6,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,27; 12,14</t>
+          <t>5,46; 12,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,53; 15,24</t>
+          <t>7,16; 15,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,5</t>
+          <t>0,36; 3,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,05; 15,75</t>
+          <t>8,19; 16,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,3; 20,73</t>
+          <t>9,27; 21,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 4,13</t>
+          <t>1,09; 3,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,65; 12,98</t>
+          <t>7,48; 12,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,14; 16,63</t>
+          <t>9,48; 16,99</t>
         </is>
       </c>
     </row>
@@ -1010,42 +1013,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,27</t>
+          <t>11,16; 15,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 17,01</t>
+          <t>11,07; 16,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,32</t>
+          <t>2,95; 5,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,81; 17,53</t>
+          <t>12,95; 17,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,4; 16,98</t>
+          <t>11,33; 17,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,2; 5,03</t>
+          <t>3,22; 5,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,53; 15,66</t>
+          <t>12,66; 15,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 15,91</t>
+          <t>11,79; 16,12</t>
         </is>
       </c>
     </row>
@@ -1069,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8824</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13879</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13794</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9328</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>15958</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7766</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>18152</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>29837</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>21560</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>5027; 13864</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>8976; 19591</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>6197; 28231</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5286; 15840</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10455; 22062</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3855; 14464</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12059; 26259</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>21969; 37863</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>12994; 37705</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>14561</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>64053</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>59849</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>18995</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>73458</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72354</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>33556</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>137511</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>132203</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8960; 22029</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>51914; 77159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45508; 75471</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>13259; 28192</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>61014; 87788</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>56106; 93396</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>25782; 45534</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>120695; 155998</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>110377; 155637</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14053</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>16050</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>21847</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>25434</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>7751</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>35900</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>41484</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2332; 11045</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9323; 20604</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10641; 23253</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>625; 5848</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>15178; 30652</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16911; 38463</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3705; 13351</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>26636; 45613</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>31379; 56221</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>28922</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>91985</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>89694</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>105554</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>59459</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>203248</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>195248</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>21329; 39146</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>78140; 107958</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>73461; 111838</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>22139; 41116</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>95798; 131128</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>86163; 130400</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>47066; 73879</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>182313; 228599</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>167889; 229499</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$notiene-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,44; 15,01</t>
+          <t>5,35; 15,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>15,28; 33,35</t>
+          <t>14,52; 33,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,33; 51,63</t>
+          <t>11,0; 48,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 18,38</t>
+          <t>5,96; 17,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 32,15</t>
+          <t>15,99; 32,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,22; 23,33</t>
+          <t>6,32; 22,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,75; 14,71</t>
+          <t>6,76; 14,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,25; 29,73</t>
+          <t>17,52; 29,89</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,14; 32,31</t>
+          <t>11,08; 32,5</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 4,91</t>
+          <t>2,11; 5,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,03; 16,39</t>
+          <t>11,21; 16,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 16,39</t>
+          <t>10,03; 16,22</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,69; 5,72</t>
+          <t>2,6; 5,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,55; 18,06</t>
+          <t>12,52; 18,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,88; 18,1</t>
+          <t>11,02; 18,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,83</t>
+          <t>2,63; 4,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,61; 16,3</t>
+          <t>12,58; 16,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,3; 15,94</t>
+          <t>11,31; 16,17</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 6,62</t>
+          <t>1,5; 6,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,46; 12,07</t>
+          <t>5,4; 12,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 15,65</t>
+          <t>6,82; 15,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,4</t>
+          <t>0,36; 3,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,19; 16,54</t>
+          <t>8,32; 16,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,27; 21,09</t>
+          <t>9,43; 20,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,94</t>
+          <t>1,14; 4,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 12,81</t>
+          <t>7,64; 13,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,48; 16,99</t>
+          <t>9,35; 17,42</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,53</t>
+          <t>2,93; 5,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,42</t>
+          <t>11,36; 15,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 16,85</t>
+          <t>10,88; 17,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,47</t>
+          <t>2,94; 5,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,95; 17,72</t>
+          <t>12,99; 17,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 17,15</t>
+          <t>11,3; 16,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 5,06</t>
+          <t>3,29; 5,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,66; 15,87</t>
+          <t>12,6; 15,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,79; 16,12</t>
+          <t>11,97; 16,0</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5027; 13864</t>
+          <t>4945; 13903</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8976; 19591</t>
+          <t>8528; 19386</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6197; 28231</t>
+          <t>6017; 26425</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5286; 15840</t>
+          <t>5134; 15341</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10455; 22062</t>
+          <t>10972; 22411</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3855; 14464</t>
+          <t>3919; 14208</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12059; 26259</t>
+          <t>12062; 26392</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21969; 37863</t>
+          <t>22310; 38066</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12994; 37705</t>
+          <t>12925; 37922</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>8960; 22029</t>
+          <t>9493; 22885</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>51914; 77159</t>
+          <t>52794; 76327</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45508; 75471</t>
+          <t>46194; 74717</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>13259; 28192</t>
+          <t>12846; 26855</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61014; 87788</t>
+          <t>60852; 87605</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56106; 93396</t>
+          <t>56838; 93551</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25782; 45534</t>
+          <t>24817; 44609</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>120695; 155998</t>
+          <t>120414; 156323</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>110377; 155637</t>
+          <t>110396; 157890</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2332; 11045</t>
+          <t>2508; 11345</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9323; 20604</t>
+          <t>9216; 20688</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10641; 23253</t>
+          <t>10127; 23338</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>625; 5848</t>
+          <t>621; 6668</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15178; 30652</t>
+          <t>15415; 30264</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>16911; 38463</t>
+          <t>17193; 37610</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3705; 13351</t>
+          <t>3873; 13856</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26636; 45613</t>
+          <t>27199; 46318</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31379; 56221</t>
+          <t>30932; 57664</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21329; 39146</t>
+          <t>20748; 37967</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>78140; 107958</t>
+          <t>79563; 105936</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>73461; 111838</t>
+          <t>72198; 113770</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22139; 41116</t>
+          <t>22097; 40810</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>95798; 131128</t>
+          <t>96101; 128502</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86163; 130400</t>
+          <t>85913; 128326</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47066; 73879</t>
+          <t>48059; 74330</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>182313; 228599</t>
+          <t>181435; 227202</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>167889; 229499</t>
+          <t>170497; 227867</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$notiene-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10,82%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>23,26%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,55%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>23,62%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>25,23%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10,82%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23,26%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,35; 15,05</t>
+          <t>6,11; 17,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,52; 33,0</t>
+          <t>14,87; 32,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,0; 48,33</t>
+          <t>5,44; 21,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,96; 17,8</t>
+          <t>5,34; 16,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,99; 32,66</t>
+          <t>15,19; 34,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,32; 22,92</t>
+          <t>7,45; 24,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,76; 14,78</t>
+          <t>7,14; 14,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,52; 29,89</t>
+          <t>17,79; 30,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,08; 32,5</t>
+          <t>7,66; 18,72</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>12,66%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3,24%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>13,61%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,11; 5,1</t>
+          <t>2,58; 5,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>11,21; 16,21</t>
+          <t>12,78; 18,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 16,22</t>
+          <t>10,09; 15,61</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,45</t>
+          <t>2,11; 4,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,52; 18,02</t>
+          <t>11,21; 16,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,02; 18,13</t>
+          <t>10,14; 15,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,63; 4,73</t>
+          <t>2,66; 4,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,58; 16,34</t>
+          <t>12,6; 16,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11,31; 16,17</t>
+          <t>10,81; 14,74</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,79%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,46%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,24%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>10,8%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,8</t>
+          <t>0,36; 3,5</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,4; 12,12</t>
+          <t>8,05; 15,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,82; 15,71</t>
+          <t>8,3; 17,6</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,87</t>
+          <t>1,42; 6,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,32; 16,33</t>
+          <t>5,27; 12,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 20,62</t>
+          <t>6,13; 14,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,09</t>
+          <t>1,16; 4,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,64; 13,01</t>
+          <t>7,65; 12,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,35; 17,42</t>
+          <t>8,5; 14,75</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>13,51%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,36</t>
+          <t>2,95; 5,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,13</t>
+          <t>12,81; 17,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,88; 17,14</t>
+          <t>10,48; 15,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,94; 5,43</t>
+          <t>3,01; 5,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,99; 17,36</t>
+          <t>11,14; 15,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 16,88</t>
+          <t>10,17; 14,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,09</t>
+          <t>3,2; 5,03</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,78</t>
+          <t>12,53; 15,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,97; 16,0</t>
+          <t>10,78; 14,04</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9328</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>15958</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6607</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>8824</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>13879</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13794</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9328</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15958</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7766</t>
+          <t>6569</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>13176</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>4945; 13903</t>
+          <t>5270; 14911</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>8528; 19386</t>
+          <t>10204; 22466</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6017; 26425</t>
+          <t>3086; 12357</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5134; 15341</t>
+          <t>4937; 14804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>10972; 22411</t>
+          <t>8923; 20082</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3919; 14208</t>
+          <t>3482; 11222</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12062; 26392</t>
+          <t>12755; 26697</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22310; 38066</t>
+          <t>22652; 38381</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12925; 37922</t>
+          <t>7930; 19372</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>97</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>83</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>18995</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73458</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60160</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>14561</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>64053</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>59849</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18995</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>73458</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72354</t>
+          <t>54633</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>132203</t>
+          <t>114793</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9493; 22885</t>
+          <t>12739; 27511</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>52794; 76327</t>
+          <t>62134; 87988</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>46194; 74717</t>
+          <t>47925; 74157</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12846; 26855</t>
+          <t>9492; 21991</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60852; 87605</t>
+          <t>52772; 76442</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56838; 93551</t>
+          <t>43864; 66686</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24817; 44609</t>
+          <t>25093; 43813</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>120414; 156323</t>
+          <t>120576; 156098</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>110396; 157890</t>
+          <t>98110; 133792</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>21847</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>20873</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>5536</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>14053</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>16050</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2214</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>21847</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25434</t>
+          <t>15398</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41484</t>
+          <t>36271</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2508; 11345</t>
+          <t>628; 6029</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9216; 20688</t>
+          <t>14921; 29191</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10127; 23338</t>
+          <t>13908; 29468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>621; 6668</t>
+          <t>2361; 11227</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15415; 30264</t>
+          <t>8998; 20722</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17193; 37610</t>
+          <t>9133; 22037</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3873; 13856</t>
+          <t>3925; 14014</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>27199; 46318</t>
+          <t>27215; 46205</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30932; 57664</t>
+          <t>26877; 46652</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>87640</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>28922</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>91985</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>89694</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>30537</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>111264</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>105554</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>195248</t>
+          <t>164240</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>20748; 37967</t>
+          <t>22197; 39990</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>79563; 105936</t>
+          <t>94773; 129732</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72198; 113770</t>
+          <t>73275; 105461</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>22097; 40810</t>
+          <t>21305; 39198</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>96101; 128502</t>
+          <t>78028; 106883</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85913; 128326</t>
+          <t>63889; 91092</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48059; 74330</t>
+          <t>46721; 73394</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>181435; 227202</t>
+          <t>180428; 225587</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>170497; 227867</t>
+          <t>143041; 186375</t>
         </is>
       </c>
     </row>
